--- a/diseases/d003/2005-2009.xlsx
+++ b/diseases/d003/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -3085,9 +3082,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3481,9 +3475,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3777,9 +3768,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4073,9 +4061,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4369,9 +4354,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4665,9 +4647,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4961,9 +4940,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5257,9 +5233,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5553,9 +5526,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5849,9 +5819,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6145,9 +6112,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6441,9 +6405,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6737,9 +6698,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7033,9 +6991,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7429,9 +7384,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7725,9 +7677,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8021,9 +7970,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8317,9 +8263,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8613,9 +8556,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8909,9 +8849,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9205,9 +9142,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9501,9 +9435,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9797,9 +9728,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10093,9 +10021,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10389,9 +10314,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10685,9 +10607,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10981,9 +10900,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11377,9 +11293,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11673,9 +11586,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11969,9 +11879,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12265,9 +12172,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12561,9 +12465,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12857,9 +12758,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13153,9 +13051,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13449,9 +13344,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13745,9 +13637,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14041,9 +13930,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14337,9 +14223,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14633,9 +14516,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14929,9 +14809,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15325,9 +15202,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15621,9 +15495,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15917,9 +15788,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16213,9 +16081,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16509,9 +16374,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16805,9 +16667,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17101,9 +16960,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17397,9 +17253,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17693,9 +17546,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17989,9 +17839,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18285,9 +18132,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18579,9 +18423,6 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">

--- a/diseases/d003/2005-2009.xlsx
+++ b/diseases/d003/2005-2009.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -776,68 +773,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -864,17 +875,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -913,17 +924,34 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Severe Acute Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -931,6 +959,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -948,7 +1034,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -961,42 +1047,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1023,17 +1109,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1072,165 +1158,79 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Córónaveirulungnabólga</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>1</v>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2005-02-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2005-02</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1306,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1317,68 +1314,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1405,17 +1416,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1440,12 +1451,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2005-03-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2005-03</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1454,79 +1465,165 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1685,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2005-04-01</t>
+          <t>2005-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2005-04</t>
+          <t>2005-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1736,12 +1833,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2005-05-01</t>
+          <t>2005-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2005-05</t>
+          <t>2005-03</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1884,12 +1981,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2005-06-01</t>
+          <t>2005-04-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2005-06</t>
+          <t>2005-04</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2032,12 +2129,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2005-07-01</t>
+          <t>2005-05-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2005-07</t>
+          <t>2005-05</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2180,12 +2277,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2005-08-01</t>
+          <t>2005-06-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2005-08</t>
+          <t>2005-06</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2328,12 +2425,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
+          <t>2005-07-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2005-09</t>
+          <t>2005-07</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2476,12 +2573,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2005-10-01</t>
+          <t>2005-08-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2005-10</t>
+          <t>2005-08</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2624,12 +2721,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2005-11-01</t>
+          <t>2005-09-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2005-11</t>
+          <t>2005-09</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2772,12 +2869,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-10-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2005-12</t>
+          <t>2005-10</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2920,12 +3017,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2005-11-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2005-11</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3038,12 +3135,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3068,12 +3165,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2005-12-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2005-12</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3082,6 +3179,9 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3090,82 +3190,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3192,17 +3278,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3241,34 +3327,17 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Córónaveirulungnabólga</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3276,64 +3345,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN18" t="b">
-        <v>1</v>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3351,7 +3362,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -3364,42 +3375,42 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3426,17 +3437,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3475,76 +3486,165 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Severe Acute Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3606,12 +3706,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3724,12 +3824,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3754,12 +3854,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3776,68 +3876,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3978,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3899,12 +4013,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3913,79 +4027,165 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4047,12 +4247,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4192,12 +4392,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4340,12 +4540,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4485,12 +4685,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4633,12 +4833,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4778,12 +4978,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-04-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4926,12 +5126,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-04-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5071,12 +5271,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5219,12 +5419,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5364,12 +5564,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5512,12 +5712,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5657,12 +5857,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5805,12 +6005,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5950,12 +6150,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6098,12 +6298,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6243,12 +6443,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6391,12 +6591,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6536,12 +6736,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6684,12 +6884,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6829,12 +7029,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6947,12 +7147,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6977,12 +7177,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6999,82 +7199,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7101,17 +7287,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7136,12 +7322,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7150,165 +7336,79 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Córónaveirulungnabólga</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN44" t="b">
-        <v>1</v>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7370,12 +7470,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7485,12 +7585,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7515,12 +7615,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7529,9 +7629,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -7540,68 +7637,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7628,17 +7739,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7663,12 +7774,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7677,76 +7788,165 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Severe Acute Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7808,12 +8008,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7926,12 +8126,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7956,12 +8156,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7978,68 +8178,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -8066,17 +8280,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8101,12 +8315,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8115,79 +8329,165 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN50" t="b">
+        <v>1</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8549,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8394,12 +8694,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8542,12 +8842,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8687,12 +8987,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8835,12 +9135,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8980,12 +9280,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -9128,12 +9428,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9273,12 +9573,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9421,12 +9721,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9566,12 +9866,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9714,12 +10014,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9859,12 +10159,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -10007,12 +10307,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10152,12 +10452,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -10300,12 +10600,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10445,12 +10745,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10593,12 +10893,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -10738,12 +11038,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -10856,12 +11156,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10886,12 +11186,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -10908,82 +11208,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11010,17 +11296,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -11045,12 +11331,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11059,165 +11345,79 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>Córónaveirulungnabólga</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN70" t="b">
-        <v>1</v>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11279,12 +11479,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11424,12 +11624,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -11572,12 +11772,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11687,12 +11887,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11717,12 +11917,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11731,9 +11931,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -11742,68 +11939,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11830,17 +12041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11865,12 +12076,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11879,76 +12090,165 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Severe Acute Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12310,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -12128,12 +12428,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -12158,12 +12458,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12180,68 +12480,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -12268,17 +12582,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12303,12 +12617,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12317,79 +12631,165 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN78" t="b">
+        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12851,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12596,12 +12996,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12744,12 +13144,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12889,12 +13289,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -13037,12 +13437,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -13182,12 +13582,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13330,12 +13730,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -13475,12 +13875,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -13623,12 +14023,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -13768,12 +14168,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13916,12 +14316,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -14061,12 +14461,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -14209,12 +14609,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -14354,12 +14754,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -14502,12 +14902,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -14647,12 +15047,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -14765,12 +15165,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14795,12 +15195,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -14817,82 +15217,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14919,17 +15305,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14954,12 +15340,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -14968,165 +15354,79 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Córónaveirulungnabólga</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN96" t="b">
-        <v>1</v>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15188,12 +15488,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -15333,12 +15633,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -15481,12 +15781,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -15626,12 +15926,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -15774,12 +16074,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -15889,12 +16189,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15919,12 +16219,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N102" t="n">
@@ -15933,9 +16233,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -15944,68 +16241,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16032,17 +16343,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -16067,12 +16378,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N103" t="n">
@@ -16081,76 +16392,165 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Severe Acute Respiratory Syndrome</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D199_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16212,12 +16612,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -16330,12 +16730,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -16360,12 +16760,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -16382,68 +16782,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -16470,17 +16884,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -16505,12 +16919,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N106" t="n">
@@ -16519,79 +16933,165 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Córónaveirulungnabólga</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>1</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SARS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -16653,12 +17153,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N107" t="n">
@@ -16798,12 +17298,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N108" t="n">
@@ -16946,12 +17446,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N109" t="n">
@@ -17091,12 +17591,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N110" t="n">
@@ -17239,12 +17739,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N111" t="n">
@@ -17384,12 +17884,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N112" t="n">
@@ -17532,12 +18032,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N113" t="n">
@@ -17677,12 +18177,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N114" t="n">
@@ -17825,12 +18325,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N115" t="n">
@@ -17970,12 +18470,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N116" t="n">
@@ -18118,12 +18618,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -18263,12 +18763,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N118" t="n">
@@ -18411,12 +18911,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N119" t="n">
@@ -18493,6 +18993,1471 @@
         </is>
       </c>
       <c r="BC119" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sars</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -18614,7 +20579,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -18624,7 +20589,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -18644,7 +20609,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -18654,7 +20619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
